--- a/config/测控柜_中车.xlsx
+++ b/config/测控柜_中车.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="800">
   <si>
     <t>序号</t>
   </si>
@@ -2400,6 +2400,9 @@
     <t>{"en":"Non electric quantity 2 action"}</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
     <t>1#低压开关遥控合分闸</t>
   </si>
   <si>
@@ -2407,6 +2410,9 @@
   </si>
   <si>
     <t>{"en":"1 # Low voltage switch remote control closing and opening"}</t>
+  </si>
+  <si>
+    <t>双点</t>
   </si>
   <si>
     <t>2#低压开关遥控合分闸</t>
@@ -2455,7 +2461,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2908,19 +2914,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2929,7 +2935,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3053,12 +3059,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3461,7 +3470,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>16385</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -3493,7 +3502,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>2</v>
+        <v>16386</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -3525,7 +3534,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="2">
-        <v>3</v>
+        <v>16387</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -3557,7 +3566,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="2">
-        <v>4</v>
+        <v>16388</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -3589,7 +3598,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="2">
-        <v>5</v>
+        <v>16389</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -3621,7 +3630,7 @@
         <v>26</v>
       </c>
       <c r="C7" s="2">
-        <v>6</v>
+        <v>16390</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -3653,7 +3662,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="2">
-        <v>7</v>
+        <v>16391</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -3685,7 +3694,7 @@
         <v>32</v>
       </c>
       <c r="C9" s="2">
-        <v>8</v>
+        <v>16392</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -3717,7 +3726,7 @@
         <v>35</v>
       </c>
       <c r="C10" s="2">
-        <v>9</v>
+        <v>16393</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -3749,7 +3758,7 @@
         <v>38</v>
       </c>
       <c r="C11" s="2">
-        <v>10</v>
+        <v>16394</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -3781,7 +3790,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="2">
-        <v>11</v>
+        <v>16395</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -3813,7 +3822,7 @@
         <v>44</v>
       </c>
       <c r="C13" s="2">
-        <v>12</v>
+        <v>16396</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
@@ -3845,7 +3854,7 @@
         <v>47</v>
       </c>
       <c r="C14" s="2">
-        <v>13</v>
+        <v>16397</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -3877,7 +3886,7 @@
         <v>50</v>
       </c>
       <c r="C15" s="2">
-        <v>14</v>
+        <v>16398</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -3909,7 +3918,7 @@
         <v>53</v>
       </c>
       <c r="C16" s="2">
-        <v>15</v>
+        <v>16399</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
@@ -3941,7 +3950,7 @@
         <v>56</v>
       </c>
       <c r="C17" s="2">
-        <v>16</v>
+        <v>16400</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
@@ -3973,7 +3982,7 @@
         <v>59</v>
       </c>
       <c r="C18" s="2">
-        <v>17</v>
+        <v>16401</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
@@ -4005,7 +4014,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="2">
-        <v>18</v>
+        <v>16402</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -4037,7 +4046,7 @@
         <v>63</v>
       </c>
       <c r="C20" s="2">
-        <v>19</v>
+        <v>16403</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
@@ -4069,7 +4078,7 @@
         <v>66</v>
       </c>
       <c r="C21" s="2">
-        <v>20</v>
+        <v>16404</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
@@ -4101,7 +4110,7 @@
         <v>69</v>
       </c>
       <c r="C22" s="2">
-        <v>21</v>
+        <v>16405</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
@@ -4133,7 +4142,7 @@
         <v>72</v>
       </c>
       <c r="C23" s="2">
-        <v>22</v>
+        <v>16406</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
@@ -4165,7 +4174,7 @@
         <v>75</v>
       </c>
       <c r="C24" s="2">
-        <v>23</v>
+        <v>16407</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
@@ -4197,7 +4206,7 @@
         <v>78</v>
       </c>
       <c r="C25" s="2">
-        <v>24</v>
+        <v>16408</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
@@ -4229,7 +4238,7 @@
         <v>81</v>
       </c>
       <c r="C26" s="2">
-        <v>25</v>
+        <v>16409</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
@@ -4261,7 +4270,7 @@
         <v>84</v>
       </c>
       <c r="C27" s="2">
-        <v>26</v>
+        <v>16410</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
@@ -4293,7 +4302,7 @@
         <v>87</v>
       </c>
       <c r="C28" s="2">
-        <v>27</v>
+        <v>16411</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
@@ -4325,7 +4334,7 @@
         <v>90</v>
       </c>
       <c r="C29" s="2">
-        <v>28</v>
+        <v>16412</v>
       </c>
       <c r="D29" s="2">
         <v>1</v>
@@ -4357,7 +4366,7 @@
         <v>93</v>
       </c>
       <c r="C30" s="2">
-        <v>29</v>
+        <v>16413</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -4389,7 +4398,7 @@
         <v>96</v>
       </c>
       <c r="C31" s="2">
-        <v>30</v>
+        <v>16414</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -4421,7 +4430,7 @@
         <v>99</v>
       </c>
       <c r="C32" s="2">
-        <v>31</v>
+        <v>16415</v>
       </c>
       <c r="D32" s="2">
         <v>1</v>
@@ -4453,7 +4462,7 @@
         <v>102</v>
       </c>
       <c r="C33" s="2">
-        <v>32</v>
+        <v>16416</v>
       </c>
       <c r="D33" s="2">
         <v>1</v>
@@ -4485,7 +4494,7 @@
         <v>105</v>
       </c>
       <c r="C34" s="2">
-        <v>33</v>
+        <v>16417</v>
       </c>
       <c r="D34" s="2">
         <v>1</v>
@@ -4517,7 +4526,7 @@
         <v>108</v>
       </c>
       <c r="C35" s="2">
-        <v>34</v>
+        <v>16418</v>
       </c>
       <c r="D35" s="2">
         <v>1</v>
@@ -4549,7 +4558,7 @@
         <v>111</v>
       </c>
       <c r="C36" s="2">
-        <v>35</v>
+        <v>16419</v>
       </c>
       <c r="D36" s="2">
         <v>1</v>
@@ -4581,7 +4590,7 @@
         <v>114</v>
       </c>
       <c r="C37" s="2">
-        <v>36</v>
+        <v>16420</v>
       </c>
       <c r="D37" s="2">
         <v>1</v>
@@ -4613,7 +4622,7 @@
         <v>117</v>
       </c>
       <c r="C38" s="2">
-        <v>37</v>
+        <v>16421</v>
       </c>
       <c r="D38" s="2">
         <v>1</v>
@@ -4645,7 +4654,7 @@
         <v>120</v>
       </c>
       <c r="C39" s="2">
-        <v>38</v>
+        <v>16422</v>
       </c>
       <c r="D39" s="2">
         <v>1</v>
@@ -4677,7 +4686,7 @@
         <v>123</v>
       </c>
       <c r="C40" s="2">
-        <v>39</v>
+        <v>16423</v>
       </c>
       <c r="D40" s="2">
         <v>1</v>
@@ -4709,7 +4718,7 @@
         <v>126</v>
       </c>
       <c r="C41" s="2">
-        <v>40</v>
+        <v>16424</v>
       </c>
       <c r="D41" s="2">
         <v>1</v>
@@ -4741,7 +4750,7 @@
         <v>129</v>
       </c>
       <c r="C42" s="2">
-        <v>41</v>
+        <v>16425</v>
       </c>
       <c r="D42" s="2">
         <v>1</v>
@@ -4773,7 +4782,7 @@
         <v>132</v>
       </c>
       <c r="C43" s="2">
-        <v>42</v>
+        <v>16426</v>
       </c>
       <c r="D43" s="2">
         <v>1</v>
@@ -4805,7 +4814,7 @@
         <v>135</v>
       </c>
       <c r="C44" s="2">
-        <v>43</v>
+        <v>16427</v>
       </c>
       <c r="D44" s="2">
         <v>1</v>
@@ -4837,7 +4846,7 @@
         <v>138</v>
       </c>
       <c r="C45" s="2">
-        <v>44</v>
+        <v>16428</v>
       </c>
       <c r="D45" s="2">
         <v>1</v>
@@ -4869,7 +4878,7 @@
         <v>141</v>
       </c>
       <c r="C46" s="2">
-        <v>45</v>
+        <v>16429</v>
       </c>
       <c r="D46" s="2">
         <v>1</v>
@@ -4901,7 +4910,7 @@
         <v>144</v>
       </c>
       <c r="C47" s="2">
-        <v>46</v>
+        <v>16430</v>
       </c>
       <c r="D47" s="2">
         <v>1</v>
@@ -4933,7 +4942,7 @@
         <v>147</v>
       </c>
       <c r="C48" s="2">
-        <v>47</v>
+        <v>16431</v>
       </c>
       <c r="D48" s="2">
         <v>1</v>
@@ -4965,7 +4974,7 @@
         <v>150</v>
       </c>
       <c r="C49" s="2">
-        <v>48</v>
+        <v>16432</v>
       </c>
       <c r="D49" s="2">
         <v>1</v>
@@ -4997,7 +5006,7 @@
         <v>153</v>
       </c>
       <c r="C50" s="2">
-        <v>49</v>
+        <v>16433</v>
       </c>
       <c r="D50" s="2">
         <v>1</v>
@@ -5029,7 +5038,7 @@
         <v>156</v>
       </c>
       <c r="C51" s="2">
-        <v>50</v>
+        <v>16434</v>
       </c>
       <c r="D51" s="2">
         <v>1</v>
@@ -5061,7 +5070,7 @@
         <v>159</v>
       </c>
       <c r="C52" s="2">
-        <v>51</v>
+        <v>16435</v>
       </c>
       <c r="D52" s="2">
         <v>1</v>
@@ -5093,7 +5102,7 @@
         <v>162</v>
       </c>
       <c r="C53" s="2">
-        <v>52</v>
+        <v>16436</v>
       </c>
       <c r="D53" s="2">
         <v>1</v>
@@ -5125,7 +5134,7 @@
         <v>165</v>
       </c>
       <c r="C54" s="2">
-        <v>53</v>
+        <v>16437</v>
       </c>
       <c r="D54" s="2">
         <v>1</v>
@@ -5157,7 +5166,7 @@
         <v>168</v>
       </c>
       <c r="C55" s="2">
-        <v>54</v>
+        <v>16438</v>
       </c>
       <c r="D55" s="2">
         <v>1</v>
@@ -5189,7 +5198,7 @@
         <v>171</v>
       </c>
       <c r="C56" s="2">
-        <v>55</v>
+        <v>16439</v>
       </c>
       <c r="D56" s="2">
         <v>1</v>
@@ -5221,7 +5230,7 @@
         <v>174</v>
       </c>
       <c r="C57" s="2">
-        <v>56</v>
+        <v>16440</v>
       </c>
       <c r="D57" s="2">
         <v>1</v>
@@ -5253,7 +5262,7 @@
         <v>177</v>
       </c>
       <c r="C58" s="2">
-        <v>57</v>
+        <v>16441</v>
       </c>
       <c r="D58" s="2">
         <v>1</v>
@@ -5285,7 +5294,7 @@
         <v>180</v>
       </c>
       <c r="C59" s="2">
-        <v>58</v>
+        <v>16442</v>
       </c>
       <c r="D59" s="2">
         <v>1</v>
@@ -5317,7 +5326,7 @@
         <v>183</v>
       </c>
       <c r="C60" s="2">
-        <v>59</v>
+        <v>16443</v>
       </c>
       <c r="D60" s="2">
         <v>1</v>
@@ -5349,7 +5358,7 @@
         <v>186</v>
       </c>
       <c r="C61" s="2">
-        <v>60</v>
+        <v>16444</v>
       </c>
       <c r="D61" s="2">
         <v>1</v>
@@ -5381,7 +5390,7 @@
         <v>189</v>
       </c>
       <c r="C62" s="2">
-        <v>61</v>
+        <v>16445</v>
       </c>
       <c r="D62" s="2">
         <v>1</v>
@@ -5413,7 +5422,7 @@
         <v>192</v>
       </c>
       <c r="C63" s="2">
-        <v>62</v>
+        <v>16446</v>
       </c>
       <c r="D63" s="2">
         <v>1</v>
@@ -5445,7 +5454,7 @@
         <v>195</v>
       </c>
       <c r="C64" s="2">
-        <v>63</v>
+        <v>16447</v>
       </c>
       <c r="D64" s="2">
         <v>1</v>
@@ -5477,7 +5486,7 @@
         <v>198</v>
       </c>
       <c r="C65" s="2">
-        <v>64</v>
+        <v>16448</v>
       </c>
       <c r="D65" s="2">
         <v>1</v>
@@ -5509,7 +5518,7 @@
         <v>201</v>
       </c>
       <c r="C66" s="2">
-        <v>65</v>
+        <v>16449</v>
       </c>
       <c r="D66" s="2">
         <v>1</v>
@@ -5541,7 +5550,7 @@
         <v>204</v>
       </c>
       <c r="C67" s="2">
-        <v>66</v>
+        <v>16450</v>
       </c>
       <c r="D67" s="2">
         <v>1</v>
@@ -5573,7 +5582,7 @@
         <v>207</v>
       </c>
       <c r="C68" s="2">
-        <v>67</v>
+        <v>16451</v>
       </c>
       <c r="D68" s="2">
         <v>1</v>
@@ -5605,7 +5614,7 @@
         <v>210</v>
       </c>
       <c r="C69" s="2">
-        <v>68</v>
+        <v>16452</v>
       </c>
       <c r="D69" s="2">
         <v>1</v>
@@ -5637,7 +5646,7 @@
         <v>213</v>
       </c>
       <c r="C70" s="2">
-        <v>69</v>
+        <v>16453</v>
       </c>
       <c r="D70" s="2">
         <v>1</v>
@@ -5669,7 +5678,7 @@
         <v>216</v>
       </c>
       <c r="C71" s="2">
-        <v>70</v>
+        <v>16454</v>
       </c>
       <c r="D71" s="2">
         <v>1</v>
@@ -5701,7 +5710,7 @@
         <v>219</v>
       </c>
       <c r="C72" s="2">
-        <v>71</v>
+        <v>16455</v>
       </c>
       <c r="D72" s="2">
         <v>1</v>
@@ -5733,7 +5742,7 @@
         <v>222</v>
       </c>
       <c r="C73" s="2">
-        <v>72</v>
+        <v>16456</v>
       </c>
       <c r="D73" s="2">
         <v>1</v>
@@ -5765,7 +5774,7 @@
         <v>225</v>
       </c>
       <c r="C74" s="2">
-        <v>73</v>
+        <v>16457</v>
       </c>
       <c r="D74" s="2">
         <v>1</v>
@@ -5797,7 +5806,7 @@
         <v>228</v>
       </c>
       <c r="C75" s="2">
-        <v>74</v>
+        <v>16458</v>
       </c>
       <c r="D75" s="2">
         <v>1</v>
@@ -5829,7 +5838,7 @@
         <v>231</v>
       </c>
       <c r="C76" s="2">
-        <v>75</v>
+        <v>16459</v>
       </c>
       <c r="D76" s="2">
         <v>1</v>
@@ -5861,7 +5870,7 @@
         <v>234</v>
       </c>
       <c r="C77" s="2">
-        <v>76</v>
+        <v>16460</v>
       </c>
       <c r="D77" s="2">
         <v>1</v>
@@ -5893,7 +5902,7 @@
         <v>237</v>
       </c>
       <c r="C78" s="2">
-        <v>77</v>
+        <v>16461</v>
       </c>
       <c r="D78" s="2">
         <v>1</v>
@@ -5925,7 +5934,7 @@
         <v>240</v>
       </c>
       <c r="C79" s="2">
-        <v>78</v>
+        <v>16462</v>
       </c>
       <c r="D79" s="2">
         <v>1</v>
@@ -5957,7 +5966,7 @@
         <v>243</v>
       </c>
       <c r="C80" s="2">
-        <v>79</v>
+        <v>16463</v>
       </c>
       <c r="D80" s="2">
         <v>1</v>
@@ -5989,7 +5998,7 @@
         <v>246</v>
       </c>
       <c r="C81" s="2">
-        <v>80</v>
+        <v>16464</v>
       </c>
       <c r="D81" s="2">
         <v>1</v>
@@ -6021,7 +6030,7 @@
         <v>249</v>
       </c>
       <c r="C82" s="2">
-        <v>81</v>
+        <v>16465</v>
       </c>
       <c r="D82" s="2">
         <v>1</v>
@@ -6053,7 +6062,7 @@
         <v>252</v>
       </c>
       <c r="C83" s="2">
-        <v>82</v>
+        <v>16466</v>
       </c>
       <c r="D83" s="2">
         <v>1</v>
@@ -6085,7 +6094,7 @@
         <v>255</v>
       </c>
       <c r="C84" s="2">
-        <v>83</v>
+        <v>16467</v>
       </c>
       <c r="D84" s="2">
         <v>1</v>
@@ -6117,7 +6126,7 @@
         <v>258</v>
       </c>
       <c r="C85" s="2">
-        <v>84</v>
+        <v>16468</v>
       </c>
       <c r="D85" s="2">
         <v>1</v>
@@ -6149,7 +6158,7 @@
         <v>261</v>
       </c>
       <c r="C86" s="2">
-        <v>85</v>
+        <v>16469</v>
       </c>
       <c r="D86" s="2">
         <v>1</v>
@@ -6181,7 +6190,7 @@
         <v>264</v>
       </c>
       <c r="C87" s="2">
-        <v>86</v>
+        <v>16470</v>
       </c>
       <c r="D87" s="2">
         <v>1</v>
@@ -6213,7 +6222,7 @@
         <v>267</v>
       </c>
       <c r="C88" s="2">
-        <v>87</v>
+        <v>16471</v>
       </c>
       <c r="D88" s="2">
         <v>1</v>
@@ -6245,7 +6254,7 @@
         <v>270</v>
       </c>
       <c r="C89" s="2">
-        <v>88</v>
+        <v>16472</v>
       </c>
       <c r="D89" s="2">
         <v>1</v>
@@ -6277,7 +6286,7 @@
         <v>273</v>
       </c>
       <c r="C90" s="2">
-        <v>89</v>
+        <v>16473</v>
       </c>
       <c r="D90" s="2">
         <v>1</v>
@@ -6309,7 +6318,7 @@
         <v>276</v>
       </c>
       <c r="C91" s="2">
-        <v>90</v>
+        <v>16474</v>
       </c>
       <c r="D91" s="2">
         <v>1</v>
@@ -6341,7 +6350,7 @@
         <v>279</v>
       </c>
       <c r="C92" s="2">
-        <v>91</v>
+        <v>16475</v>
       </c>
       <c r="D92" s="2">
         <v>1</v>
@@ -6373,7 +6382,7 @@
         <v>282</v>
       </c>
       <c r="C93" s="2">
-        <v>92</v>
+        <v>16476</v>
       </c>
       <c r="D93" s="2">
         <v>1</v>
@@ -6405,7 +6414,7 @@
         <v>285</v>
       </c>
       <c r="C94" s="2">
-        <v>93</v>
+        <v>16477</v>
       </c>
       <c r="D94" s="2">
         <v>1</v>
@@ -6437,7 +6446,7 @@
         <v>288</v>
       </c>
       <c r="C95" s="2">
-        <v>94</v>
+        <v>16478</v>
       </c>
       <c r="D95" s="2">
         <v>1</v>
@@ -6469,7 +6478,7 @@
         <v>291</v>
       </c>
       <c r="C96" s="2">
-        <v>95</v>
+        <v>16479</v>
       </c>
       <c r="D96" s="2">
         <v>1</v>
@@ -6501,7 +6510,7 @@
         <v>294</v>
       </c>
       <c r="C97" s="2">
-        <v>96</v>
+        <v>16480</v>
       </c>
       <c r="D97" s="2">
         <v>1</v>
@@ -6533,7 +6542,7 @@
         <v>297</v>
       </c>
       <c r="C98" s="2">
-        <v>97</v>
+        <v>16481</v>
       </c>
       <c r="D98" s="2">
         <v>1</v>
@@ -6565,7 +6574,7 @@
         <v>300</v>
       </c>
       <c r="C99" s="2">
-        <v>98</v>
+        <v>16482</v>
       </c>
       <c r="D99" s="2">
         <v>1</v>
@@ -6597,7 +6606,7 @@
         <v>303</v>
       </c>
       <c r="C100" s="2">
-        <v>99</v>
+        <v>16483</v>
       </c>
       <c r="D100" s="2">
         <v>1</v>
@@ -6629,7 +6638,7 @@
         <v>306</v>
       </c>
       <c r="C101" s="2">
-        <v>100</v>
+        <v>16484</v>
       </c>
       <c r="D101" s="2">
         <v>1</v>
@@ -6661,7 +6670,7 @@
         <v>309</v>
       </c>
       <c r="C102" s="2">
-        <v>101</v>
+        <v>16485</v>
       </c>
       <c r="D102" s="2">
         <v>1</v>
@@ -6693,7 +6702,7 @@
         <v>312</v>
       </c>
       <c r="C103" s="2">
-        <v>102</v>
+        <v>16486</v>
       </c>
       <c r="D103" s="2">
         <v>1</v>
@@ -6725,7 +6734,7 @@
         <v>315</v>
       </c>
       <c r="C104" s="2">
-        <v>103</v>
+        <v>16487</v>
       </c>
       <c r="D104" s="2">
         <v>1</v>
@@ -6757,7 +6766,7 @@
         <v>318</v>
       </c>
       <c r="C105" s="2">
-        <v>104</v>
+        <v>16488</v>
       </c>
       <c r="D105" s="2">
         <v>1</v>
@@ -6789,7 +6798,7 @@
         <v>321</v>
       </c>
       <c r="C106" s="2">
-        <v>105</v>
+        <v>16489</v>
       </c>
       <c r="D106" s="2">
         <v>1</v>
@@ -6821,7 +6830,7 @@
         <v>324</v>
       </c>
       <c r="C107" s="2">
-        <v>106</v>
+        <v>16490</v>
       </c>
       <c r="D107" s="2">
         <v>1</v>
@@ -6853,7 +6862,7 @@
         <v>327</v>
       </c>
       <c r="C108" s="2">
-        <v>107</v>
+        <v>16491</v>
       </c>
       <c r="D108" s="2">
         <v>1</v>
@@ -6885,7 +6894,7 @@
         <v>330</v>
       </c>
       <c r="C109" s="2">
-        <v>108</v>
+        <v>16492</v>
       </c>
       <c r="D109" s="2">
         <v>1</v>
@@ -6917,7 +6926,7 @@
         <v>333</v>
       </c>
       <c r="C110" s="2">
-        <v>109</v>
+        <v>16493</v>
       </c>
       <c r="D110" s="2">
         <v>1</v>
@@ -6949,7 +6958,7 @@
         <v>336</v>
       </c>
       <c r="C111" s="2">
-        <v>110</v>
+        <v>16494</v>
       </c>
       <c r="D111" s="2">
         <v>1</v>
@@ -6981,7 +6990,7 @@
         <v>339</v>
       </c>
       <c r="C112" s="2">
-        <v>111</v>
+        <v>16495</v>
       </c>
       <c r="D112" s="2">
         <v>1</v>
@@ -7013,7 +7022,7 @@
         <v>342</v>
       </c>
       <c r="C113" s="2">
-        <v>112</v>
+        <v>16496</v>
       </c>
       <c r="D113" s="2">
         <v>1</v>
@@ -7045,7 +7054,7 @@
         <v>345</v>
       </c>
       <c r="C114" s="2">
-        <v>113</v>
+        <v>16497</v>
       </c>
       <c r="D114" s="2">
         <v>1</v>
@@ -7077,7 +7086,7 @@
         <v>348</v>
       </c>
       <c r="C115" s="2">
-        <v>114</v>
+        <v>16498</v>
       </c>
       <c r="D115" s="2">
         <v>1</v>
@@ -7109,7 +7118,7 @@
         <v>351</v>
       </c>
       <c r="C116" s="2">
-        <v>115</v>
+        <v>16499</v>
       </c>
       <c r="D116" s="2">
         <v>1</v>
@@ -7141,7 +7150,7 @@
         <v>354</v>
       </c>
       <c r="C117" s="2">
-        <v>116</v>
+        <v>16500</v>
       </c>
       <c r="D117" s="2">
         <v>1</v>
@@ -7173,7 +7182,7 @@
         <v>357</v>
       </c>
       <c r="C118" s="2">
-        <v>117</v>
+        <v>16501</v>
       </c>
       <c r="D118" s="2">
         <v>1</v>
@@ -7205,7 +7214,7 @@
         <v>360</v>
       </c>
       <c r="C119" s="2">
-        <v>118</v>
+        <v>16502</v>
       </c>
       <c r="D119" s="2">
         <v>1</v>
@@ -7237,7 +7246,7 @@
         <v>363</v>
       </c>
       <c r="C120" s="2">
-        <v>119</v>
+        <v>16503</v>
       </c>
       <c r="D120" s="2">
         <v>1</v>
@@ -7269,7 +7278,7 @@
         <v>366</v>
       </c>
       <c r="C121" s="2">
-        <v>120</v>
+        <v>16504</v>
       </c>
       <c r="D121" s="2">
         <v>1</v>
@@ -7301,7 +7310,7 @@
         <v>369</v>
       </c>
       <c r="C122" s="2">
-        <v>121</v>
+        <v>16505</v>
       </c>
       <c r="D122" s="2">
         <v>1</v>
@@ -7333,7 +7342,7 @@
         <v>372</v>
       </c>
       <c r="C123" s="2">
-        <v>122</v>
+        <v>16506</v>
       </c>
       <c r="D123" s="2">
         <v>1</v>
@@ -7365,7 +7374,7 @@
         <v>375</v>
       </c>
       <c r="C124" s="2">
-        <v>123</v>
+        <v>16507</v>
       </c>
       <c r="D124" s="2">
         <v>1</v>
@@ -7397,7 +7406,7 @@
         <v>378</v>
       </c>
       <c r="C125" s="2">
-        <v>124</v>
+        <v>16508</v>
       </c>
       <c r="D125" s="2">
         <v>1</v>
@@ -7429,7 +7438,7 @@
         <v>381</v>
       </c>
       <c r="C126" s="2">
-        <v>125</v>
+        <v>16509</v>
       </c>
       <c r="D126" s="2">
         <v>1</v>
@@ -7461,7 +7470,7 @@
         <v>384</v>
       </c>
       <c r="C127" s="2">
-        <v>126</v>
+        <v>16510</v>
       </c>
       <c r="D127" s="2">
         <v>1</v>
@@ -7493,7 +7502,7 @@
         <v>387</v>
       </c>
       <c r="C128" s="2">
-        <v>127</v>
+        <v>16511</v>
       </c>
       <c r="D128" s="2">
         <v>1</v>
@@ -7525,7 +7534,7 @@
         <v>390</v>
       </c>
       <c r="C129" s="2">
-        <v>128</v>
+        <v>16512</v>
       </c>
       <c r="D129" s="2">
         <v>1</v>
@@ -7557,7 +7566,7 @@
         <v>393</v>
       </c>
       <c r="C130" s="2">
-        <v>129</v>
+        <v>16513</v>
       </c>
       <c r="D130" s="2">
         <v>1</v>
@@ -7589,7 +7598,7 @@
         <v>396</v>
       </c>
       <c r="C131" s="2">
-        <v>130</v>
+        <v>16514</v>
       </c>
       <c r="D131" s="2">
         <v>1</v>
@@ -7621,7 +7630,7 @@
         <v>399</v>
       </c>
       <c r="C132" s="2">
-        <v>131</v>
+        <v>16515</v>
       </c>
       <c r="D132" s="2">
         <v>1</v>
@@ -7653,7 +7662,7 @@
         <v>402</v>
       </c>
       <c r="C133" s="2">
-        <v>132</v>
+        <v>16516</v>
       </c>
       <c r="D133" s="2">
         <v>1</v>
@@ -7685,7 +7694,7 @@
         <v>405</v>
       </c>
       <c r="C134" s="2">
-        <v>133</v>
+        <v>16517</v>
       </c>
       <c r="D134" s="2">
         <v>1</v>
@@ -7717,7 +7726,7 @@
         <v>408</v>
       </c>
       <c r="C135" s="2">
-        <v>134</v>
+        <v>16518</v>
       </c>
       <c r="D135" s="2">
         <v>1</v>
@@ -7749,7 +7758,7 @@
         <v>411</v>
       </c>
       <c r="C136" s="2">
-        <v>135</v>
+        <v>16519</v>
       </c>
       <c r="D136" s="2">
         <v>1</v>
@@ -7781,7 +7790,7 @@
         <v>414</v>
       </c>
       <c r="C137" s="2">
-        <v>136</v>
+        <v>16520</v>
       </c>
       <c r="D137" s="2">
         <v>1</v>
@@ -7813,7 +7822,7 @@
         <v>417</v>
       </c>
       <c r="C138" s="2">
-        <v>137</v>
+        <v>16521</v>
       </c>
       <c r="D138" s="2">
         <v>1</v>
@@ -7845,7 +7854,7 @@
         <v>420</v>
       </c>
       <c r="C139" s="2">
-        <v>138</v>
+        <v>16522</v>
       </c>
       <c r="D139" s="2">
         <v>1</v>
@@ -7877,7 +7886,7 @@
         <v>423</v>
       </c>
       <c r="C140" s="2">
-        <v>139</v>
+        <v>16523</v>
       </c>
       <c r="D140" s="2">
         <v>1</v>
@@ -7909,7 +7918,7 @@
         <v>426</v>
       </c>
       <c r="C141" s="2">
-        <v>140</v>
+        <v>16524</v>
       </c>
       <c r="D141" s="2">
         <v>1</v>
@@ -7941,7 +7950,7 @@
         <v>429</v>
       </c>
       <c r="C142" s="2">
-        <v>141</v>
+        <v>16525</v>
       </c>
       <c r="D142" s="2">
         <v>1</v>
@@ -7973,7 +7982,7 @@
         <v>432</v>
       </c>
       <c r="C143" s="2">
-        <v>142</v>
+        <v>16526</v>
       </c>
       <c r="D143" s="2">
         <v>1</v>
@@ -8005,7 +8014,7 @@
         <v>435</v>
       </c>
       <c r="C144" s="2">
-        <v>143</v>
+        <v>16527</v>
       </c>
       <c r="D144" s="2">
         <v>1</v>
@@ -8037,7 +8046,7 @@
         <v>438</v>
       </c>
       <c r="C145" s="2">
-        <v>144</v>
+        <v>16528</v>
       </c>
       <c r="D145" s="2">
         <v>1</v>
@@ -8069,7 +8078,7 @@
         <v>441</v>
       </c>
       <c r="C146" s="2">
-        <v>145</v>
+        <v>16529</v>
       </c>
       <c r="D146" s="2">
         <v>1</v>
@@ -8101,7 +8110,7 @@
         <v>444</v>
       </c>
       <c r="C147" s="2">
-        <v>146</v>
+        <v>16530</v>
       </c>
       <c r="D147" s="2">
         <v>1</v>
@@ -8133,7 +8142,7 @@
         <v>447</v>
       </c>
       <c r="C148" s="2">
-        <v>147</v>
+        <v>16531</v>
       </c>
       <c r="D148" s="2">
         <v>1</v>
@@ -8165,7 +8174,7 @@
         <v>450</v>
       </c>
       <c r="C149" s="2">
-        <v>148</v>
+        <v>16532</v>
       </c>
       <c r="D149" s="2">
         <v>1</v>
@@ -8197,7 +8206,7 @@
         <v>453</v>
       </c>
       <c r="C150" s="2">
-        <v>149</v>
+        <v>16533</v>
       </c>
       <c r="D150" s="2">
         <v>1</v>
@@ -8229,7 +8238,7 @@
         <v>456</v>
       </c>
       <c r="C151" s="2">
-        <v>150</v>
+        <v>16534</v>
       </c>
       <c r="D151" s="2">
         <v>1</v>
@@ -8261,7 +8270,7 @@
         <v>459</v>
       </c>
       <c r="C152" s="2">
-        <v>151</v>
+        <v>16535</v>
       </c>
       <c r="D152" s="2">
         <v>1</v>
@@ -8293,7 +8302,7 @@
         <v>462</v>
       </c>
       <c r="C153" s="2">
-        <v>152</v>
+        <v>16536</v>
       </c>
       <c r="D153" s="2">
         <v>1</v>
@@ -8325,7 +8334,7 @@
         <v>465</v>
       </c>
       <c r="C154" s="2">
-        <v>153</v>
+        <v>16537</v>
       </c>
       <c r="D154" s="2">
         <v>1</v>
@@ -8357,7 +8366,7 @@
         <v>468</v>
       </c>
       <c r="C155" s="2">
-        <v>154</v>
+        <v>16538</v>
       </c>
       <c r="D155" s="2">
         <v>1</v>
@@ -8389,7 +8398,7 @@
         <v>471</v>
       </c>
       <c r="C156" s="2">
-        <v>155</v>
+        <v>16539</v>
       </c>
       <c r="D156" s="2">
         <v>1</v>
@@ -8421,7 +8430,7 @@
         <v>474</v>
       </c>
       <c r="C157" s="2">
-        <v>156</v>
+        <v>16540</v>
       </c>
       <c r="D157" s="2">
         <v>1</v>
@@ -8453,7 +8462,7 @@
         <v>477</v>
       </c>
       <c r="C158" s="2">
-        <v>157</v>
+        <v>16541</v>
       </c>
       <c r="D158" s="2">
         <v>1</v>
@@ -8485,7 +8494,7 @@
         <v>480</v>
       </c>
       <c r="C159" s="2">
-        <v>158</v>
+        <v>16542</v>
       </c>
       <c r="D159" s="2">
         <v>1</v>
@@ -8517,7 +8526,7 @@
         <v>483</v>
       </c>
       <c r="C160" s="2">
-        <v>159</v>
+        <v>16543</v>
       </c>
       <c r="D160" s="2">
         <v>1</v>
@@ -8549,7 +8558,7 @@
         <v>486</v>
       </c>
       <c r="C161" s="2">
-        <v>160</v>
+        <v>16544</v>
       </c>
       <c r="D161" s="2">
         <v>1</v>
@@ -8581,7 +8590,7 @@
         <v>489</v>
       </c>
       <c r="C162" s="2">
-        <v>161</v>
+        <v>16545</v>
       </c>
       <c r="D162" s="2">
         <v>1</v>
@@ -8613,7 +8622,7 @@
         <v>492</v>
       </c>
       <c r="C163" s="2">
-        <v>162</v>
+        <v>16546</v>
       </c>
       <c r="D163" s="2">
         <v>1</v>
@@ -8645,7 +8654,7 @@
         <v>495</v>
       </c>
       <c r="C164" s="2">
-        <v>163</v>
+        <v>16547</v>
       </c>
       <c r="D164" s="2">
         <v>1</v>
@@ -8677,7 +8686,7 @@
         <v>498</v>
       </c>
       <c r="C165" s="2">
-        <v>164</v>
+        <v>16548</v>
       </c>
       <c r="D165" s="2">
         <v>1</v>
@@ -8709,7 +8718,7 @@
         <v>501</v>
       </c>
       <c r="C166" s="2">
-        <v>165</v>
+        <v>16549</v>
       </c>
       <c r="D166" s="2">
         <v>1</v>
@@ -8741,7 +8750,7 @@
         <v>504</v>
       </c>
       <c r="C167" s="2">
-        <v>166</v>
+        <v>16550</v>
       </c>
       <c r="D167" s="2">
         <v>1</v>
@@ -8773,7 +8782,7 @@
         <v>507</v>
       </c>
       <c r="C168" s="2">
-        <v>167</v>
+        <v>16551</v>
       </c>
       <c r="D168" s="2">
         <v>1</v>
@@ -8805,7 +8814,7 @@
         <v>510</v>
       </c>
       <c r="C169" s="2">
-        <v>168</v>
+        <v>16552</v>
       </c>
       <c r="D169" s="2">
         <v>1</v>
@@ -8837,7 +8846,7 @@
         <v>513</v>
       </c>
       <c r="C170" s="2">
-        <v>169</v>
+        <v>16553</v>
       </c>
       <c r="D170" s="2">
         <v>1</v>
@@ -8873,12 +8882,12 @@
   <dimension ref="A1:J109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="25.2063492063492" style="3" customWidth="1"/>
-    <col min="3" max="8" width="9" style="3"/>
-    <col min="9" max="9" width="57.6904761904762" style="3" customWidth="1"/>
-    <col min="10" max="10" width="70.531746031746" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="25.2063492063492" style="4" customWidth="1"/>
+    <col min="3" max="8" width="9" style="4"/>
+    <col min="9" max="9" width="57.6904761904762" style="4" customWidth="1"/>
+    <col min="10" max="10" width="70.531746031746" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
@@ -8914,3458 +8923,3458 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>1000</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>1001</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <v>2</v>
       </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="D3" s="4">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>1002</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="4">
         <v>3</v>
       </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
         <v>1003</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="4">
         <v>4</v>
       </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>1004</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>5</v>
       </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="4" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="3">
+      <c r="A7" s="4">
         <v>1005</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="4">
         <v>6</v>
       </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="4" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3">
+      <c r="A8" s="4">
         <v>1006</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>7</v>
       </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="4" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3">
+      <c r="A9" s="4">
         <v>1007</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="4">
         <v>8</v>
       </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="4" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="3">
+      <c r="A10" s="4">
         <v>1008</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>9</v>
       </c>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="4" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="3">
+      <c r="A11" s="4">
         <v>1009</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="4">
         <v>10</v>
       </c>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="4" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="3">
+      <c r="A12" s="4">
         <v>1010</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="C12" s="3">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="C12" s="4">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="4" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="3">
+      <c r="A13" s="4">
         <v>1011</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="4">
         <v>12</v>
       </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="4" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="3">
+      <c r="A14" s="4">
         <v>1012</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="4">
         <v>13</v>
       </c>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="4" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="3">
+      <c r="A15" s="4">
         <v>1013</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="4">
         <v>14</v>
       </c>
-      <c r="D15" s="3">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="4" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="3">
+      <c r="A16" s="4">
         <v>1014</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="4">
         <v>15</v>
       </c>
-      <c r="D16" s="3">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="4" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="3">
+      <c r="A17" s="4">
         <v>1015</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="4">
         <v>16</v>
       </c>
-      <c r="D17" s="3">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="4" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="3">
+      <c r="A18" s="4">
         <v>1016</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="4">
         <v>17</v>
       </c>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="4" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="3">
+      <c r="A19" s="4">
         <v>1017</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="4">
         <v>18</v>
       </c>
-      <c r="D19" s="3">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="4" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="3">
+      <c r="A20" s="4">
         <v>1018</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="4">
         <v>19</v>
       </c>
-      <c r="D20" s="3">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="4" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="3">
+      <c r="A21" s="4">
         <v>1019</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="4">
         <v>20</v>
       </c>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="4" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="3">
+      <c r="A22" s="4">
         <v>1020</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="4">
         <v>21</v>
       </c>
-      <c r="D22" s="3">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="4" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="3">
+      <c r="A23" s="4">
         <v>1021</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="4">
         <v>22</v>
       </c>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="4" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="3">
+      <c r="A24" s="4">
         <v>1022</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="4">
         <v>23</v>
       </c>
-      <c r="D24" s="3">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="J24" s="4" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="3">
+      <c r="A25" s="4">
         <v>1023</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="4">
         <v>24</v>
       </c>
-      <c r="D25" s="3">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="J25" s="4" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="3">
+      <c r="A26" s="4">
         <v>1024</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="4">
         <v>25</v>
       </c>
-      <c r="D26" s="3">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="J26" s="4" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="3">
+      <c r="A27" s="4">
         <v>1025</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="4">
         <v>26</v>
       </c>
-      <c r="D27" s="3">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="J27" s="4" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="3">
+      <c r="A28" s="4">
         <v>1026</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="4">
         <v>27</v>
       </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28" s="3" t="s">
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="J28" s="4" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="3">
+      <c r="A29" s="4">
         <v>1027</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="4">
         <v>28</v>
       </c>
-      <c r="D29" s="3">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="J29" s="4" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="3">
+      <c r="A30" s="4">
         <v>1028</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="4">
         <v>29</v>
       </c>
-      <c r="D30" s="3">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I30" s="3" t="s">
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="J30" s="4" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="3">
+      <c r="A31" s="4">
         <v>1029</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="4">
         <v>30</v>
       </c>
-      <c r="D31" s="3">
-        <v>1</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="4" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="3">
+      <c r="A32" s="4">
         <v>1030</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="4">
         <v>31</v>
       </c>
-      <c r="D32" s="3">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="3">
+      <c r="A33" s="4">
         <v>1031</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="4">
         <v>32</v>
       </c>
-      <c r="D33" s="3">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I33" s="3" t="s">
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="J33" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="3">
+      <c r="A34" s="4">
         <v>1032</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="4">
         <v>33</v>
       </c>
-      <c r="D34" s="3">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" s="3" t="s">
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J34" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="3">
+      <c r="A35" s="4">
         <v>1033</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="4">
         <v>34</v>
       </c>
-      <c r="D35" s="3">
-        <v>1</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I35" s="3" t="s">
+      <c r="D35" s="4">
+        <v>1</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="3">
+      <c r="A36" s="4">
         <v>1034</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="4">
         <v>35</v>
       </c>
-      <c r="D36" s="3">
-        <v>1</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I36" s="3" t="s">
+      <c r="D36" s="4">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J36" s="4" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="3">
+      <c r="A37" s="4">
         <v>1035</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="4">
         <v>36</v>
       </c>
-      <c r="D37" s="3">
-        <v>1</v>
-      </c>
-      <c r="E37" s="3">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I37" s="3" t="s">
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="J37" s="4" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="3">
+      <c r="A38" s="4">
         <v>1036</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="4">
         <v>37</v>
       </c>
-      <c r="D38" s="3">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3">
-        <v>0</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I38" s="3" t="s">
+      <c r="D38" s="4">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="4" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="3">
+      <c r="A39" s="4">
         <v>1037</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="4">
         <v>38</v>
       </c>
-      <c r="D39" s="3">
-        <v>1</v>
-      </c>
-      <c r="E39" s="3">
-        <v>0</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I39" s="3" t="s">
+      <c r="D39" s="4">
+        <v>1</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="J39" s="4" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="3">
+      <c r="A40" s="4">
         <v>1038</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="4">
         <v>39</v>
       </c>
-      <c r="D40" s="3">
-        <v>1</v>
-      </c>
-      <c r="E40" s="3">
-        <v>0</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I40" s="3" t="s">
+      <c r="D40" s="4">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="J40" s="4" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="3">
+      <c r="A41" s="4">
         <v>1039</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="4">
         <v>40</v>
       </c>
-      <c r="D41" s="3">
-        <v>1</v>
-      </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I41" s="3" t="s">
+      <c r="D41" s="4">
+        <v>1</v>
+      </c>
+      <c r="E41" s="4">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="J41" s="4" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="3">
+      <c r="A42" s="4">
         <v>1040</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="4">
         <v>41</v>
       </c>
-      <c r="D42" s="3">
-        <v>1</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I42" s="3" t="s">
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="J42" s="4" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="3">
+      <c r="A43" s="4">
         <v>1041</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="4">
         <v>42</v>
       </c>
-      <c r="D43" s="3">
-        <v>1</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I43" s="3" t="s">
+      <c r="D43" s="4">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J43" s="4" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="3">
+      <c r="A44" s="4">
         <v>1042</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="4">
         <v>43</v>
       </c>
-      <c r="D44" s="3">
-        <v>1</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I44" s="3" t="s">
+      <c r="D44" s="4">
+        <v>1</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="J44" s="4" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="3">
+      <c r="A45" s="4">
         <v>1043</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="4">
         <v>44</v>
       </c>
-      <c r="D45" s="3">
-        <v>1</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I45" s="3" t="s">
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="4">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="J45" s="4" t="s">
         <v>636</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="3">
+      <c r="A46" s="4">
         <v>1044</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="4">
         <v>45</v>
       </c>
-      <c r="D46" s="3">
-        <v>1</v>
-      </c>
-      <c r="E46" s="3">
-        <v>0</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I46" s="3" t="s">
+      <c r="D46" s="4">
+        <v>1</v>
+      </c>
+      <c r="E46" s="4">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I46" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="J46" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="3">
+      <c r="A47" s="4">
         <v>1045</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="4">
         <v>46</v>
       </c>
-      <c r="D47" s="3">
-        <v>1</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I47" s="3" t="s">
+      <c r="D47" s="4">
+        <v>1</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="J47" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="3">
+      <c r="A48" s="4">
         <v>1046</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="4">
         <v>47</v>
       </c>
-      <c r="D48" s="3">
-        <v>1</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I48" s="3" t="s">
+      <c r="D48" s="4">
+        <v>1</v>
+      </c>
+      <c r="E48" s="4">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="J48" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="3">
+      <c r="A49" s="4">
         <v>1047</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="4">
         <v>48</v>
       </c>
-      <c r="D49" s="3">
-        <v>1</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I49" s="3" t="s">
+      <c r="D49" s="4">
+        <v>1</v>
+      </c>
+      <c r="E49" s="4">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="J49" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="3">
+      <c r="A50" s="4">
         <v>1048</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="4">
         <v>49</v>
       </c>
-      <c r="D50" s="3">
-        <v>1</v>
-      </c>
-      <c r="E50" s="3">
-        <v>0</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I50" s="3" t="s">
+      <c r="D50" s="4">
+        <v>1</v>
+      </c>
+      <c r="E50" s="4">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I50" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="J50" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="3">
+      <c r="A51" s="4">
         <v>1049</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="4">
         <v>50</v>
       </c>
-      <c r="D51" s="3">
-        <v>1</v>
-      </c>
-      <c r="E51" s="3">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I51" s="3" t="s">
+      <c r="D51" s="4">
+        <v>1</v>
+      </c>
+      <c r="E51" s="4">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I51" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="J51" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="3">
+      <c r="A52" s="4">
         <v>1050</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="4">
         <v>51</v>
       </c>
-      <c r="D52" s="3">
-        <v>1</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I52" s="3" t="s">
+      <c r="D52" s="4">
+        <v>1</v>
+      </c>
+      <c r="E52" s="4">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I52" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="J52" s="4" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="3">
+      <c r="A53" s="4">
         <v>1051</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="4">
         <v>52</v>
       </c>
-      <c r="D53" s="3">
-        <v>1</v>
-      </c>
-      <c r="E53" s="3">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I53" s="3" t="s">
+      <c r="D53" s="4">
+        <v>1</v>
+      </c>
+      <c r="E53" s="4">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I53" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="J53" s="4" t="s">
         <v>642</v>
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="3">
+      <c r="A54" s="4">
         <v>1052</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="4">
         <v>53</v>
       </c>
-      <c r="D54" s="3">
-        <v>1</v>
-      </c>
-      <c r="E54" s="3">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I54" s="3" t="s">
+      <c r="D54" s="4">
+        <v>1</v>
+      </c>
+      <c r="E54" s="4">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J54" s="4" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="3">
+      <c r="A55" s="4">
         <v>1053</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="4">
         <v>54</v>
       </c>
-      <c r="D55" s="3">
-        <v>1</v>
-      </c>
-      <c r="E55" s="3">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I55" s="3" t="s">
+      <c r="D55" s="4">
+        <v>1</v>
+      </c>
+      <c r="E55" s="4">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="J55" s="4" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="3">
+      <c r="A56" s="4">
         <v>1054</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="4">
         <v>55</v>
       </c>
-      <c r="D56" s="3">
-        <v>1</v>
-      </c>
-      <c r="E56" s="3">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I56" s="3" t="s">
+      <c r="D56" s="4">
+        <v>1</v>
+      </c>
+      <c r="E56" s="4">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I56" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="J56" s="4" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="3">
+      <c r="A57" s="4">
         <v>1055</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="4">
         <v>56</v>
       </c>
-      <c r="D57" s="3">
-        <v>1</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I57" s="3" t="s">
+      <c r="D57" s="4">
+        <v>1</v>
+      </c>
+      <c r="E57" s="4">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="J57" s="4" t="s">
         <v>654</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="3">
+      <c r="A58" s="4">
         <v>1056</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="4">
         <v>57</v>
       </c>
-      <c r="D58" s="3">
-        <v>1</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I58" s="3" t="s">
+      <c r="D58" s="4">
+        <v>1</v>
+      </c>
+      <c r="E58" s="4">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="J58" s="4" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="3">
+      <c r="A59" s="4">
         <v>1057</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="4">
         <v>58</v>
       </c>
-      <c r="D59" s="3">
-        <v>1</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I59" s="3" t="s">
+      <c r="D59" s="4">
+        <v>1</v>
+      </c>
+      <c r="E59" s="4">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="J59" s="4" t="s">
         <v>660</v>
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="3">
+      <c r="A60" s="4">
         <v>1058</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="4">
         <v>59</v>
       </c>
-      <c r="D60" s="3">
-        <v>1</v>
-      </c>
-      <c r="E60" s="3">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I60" s="3" t="s">
+      <c r="D60" s="4">
+        <v>1</v>
+      </c>
+      <c r="E60" s="4">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="J60" s="3" t="s">
+      <c r="J60" s="4" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="3">
+      <c r="A61" s="4">
         <v>1059</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="4">
         <v>60</v>
       </c>
-      <c r="D61" s="3">
-        <v>1</v>
-      </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I61" s="3" t="s">
+      <c r="D61" s="4">
+        <v>1</v>
+      </c>
+      <c r="E61" s="4">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" s="4" t="s">
         <v>665</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="J61" s="4" t="s">
         <v>666</v>
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="3">
+      <c r="A62" s="4">
         <v>1060</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="4">
         <v>61</v>
       </c>
-      <c r="D62" s="3">
-        <v>1</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I62" s="3" t="s">
+      <c r="D62" s="4">
+        <v>1</v>
+      </c>
+      <c r="E62" s="4">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I62" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="J62" s="4" t="s">
         <v>668</v>
       </c>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="3">
+      <c r="A63" s="4">
         <v>1061</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="4">
         <v>62</v>
       </c>
-      <c r="D63" s="3">
-        <v>1</v>
-      </c>
-      <c r="E63" s="3">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I63" s="3" t="s">
+      <c r="D63" s="4">
+        <v>1</v>
+      </c>
+      <c r="E63" s="4">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I63" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="J63" s="3" t="s">
+      <c r="J63" s="4" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="3">
+      <c r="A64" s="4">
         <v>1062</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="4">
         <v>63</v>
       </c>
-      <c r="D64" s="3">
-        <v>1</v>
-      </c>
-      <c r="E64" s="3">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I64" s="3" t="s">
+      <c r="D64" s="4">
+        <v>1</v>
+      </c>
+      <c r="E64" s="4">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I64" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="J64" s="3" t="s">
+      <c r="J64" s="4" t="s">
         <v>674</v>
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="3">
+      <c r="A65" s="4">
         <v>1063</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="4">
         <v>64</v>
       </c>
-      <c r="D65" s="3">
-        <v>1</v>
-      </c>
-      <c r="E65" s="3">
-        <v>0</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I65" s="3" t="s">
+      <c r="D65" s="4">
+        <v>1</v>
+      </c>
+      <c r="E65" s="4">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I65" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="J65" s="4" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="3">
+      <c r="A66" s="4">
         <v>1064</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="4">
         <v>65</v>
       </c>
-      <c r="D66" s="3">
-        <v>1</v>
-      </c>
-      <c r="E66" s="3">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I66" s="3" t="s">
+      <c r="D66" s="4">
+        <v>1</v>
+      </c>
+      <c r="E66" s="4">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I66" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="J66" s="4" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="3">
+      <c r="A67" s="4">
         <v>1065</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="4">
         <v>66</v>
       </c>
-      <c r="D67" s="3">
-        <v>1</v>
-      </c>
-      <c r="E67" s="3">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I67" s="3" t="s">
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I67" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="J67" s="4" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="3">
+      <c r="A68" s="4">
         <v>1066</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="4">
         <v>67</v>
       </c>
-      <c r="D68" s="3">
-        <v>1</v>
-      </c>
-      <c r="E68" s="3">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I68" s="3" t="s">
+      <c r="D68" s="4">
+        <v>1</v>
+      </c>
+      <c r="E68" s="4">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I68" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="J68" s="4" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="3">
+      <c r="A69" s="4">
         <v>1067</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="4">
         <v>68</v>
       </c>
-      <c r="D69" s="3">
-        <v>1</v>
-      </c>
-      <c r="E69" s="3">
-        <v>0</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I69" s="3" t="s">
+      <c r="D69" s="4">
+        <v>1</v>
+      </c>
+      <c r="E69" s="4">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I69" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="J69" s="4" t="s">
         <v>682</v>
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="3">
+      <c r="A70" s="4">
         <v>1068</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="4" t="s">
         <v>683</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="4">
         <v>69</v>
       </c>
-      <c r="D70" s="3">
-        <v>1</v>
-      </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I70" s="3" t="s">
+      <c r="D70" s="4">
+        <v>1</v>
+      </c>
+      <c r="E70" s="4">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I70" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="J70" s="3" t="s">
+      <c r="J70" s="4" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="3">
+      <c r="A71" s="4">
         <v>1069</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="4">
         <v>70</v>
       </c>
-      <c r="D71" s="3">
-        <v>1</v>
-      </c>
-      <c r="E71" s="3">
-        <v>0</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I71" s="3" t="s">
+      <c r="D71" s="4">
+        <v>1</v>
+      </c>
+      <c r="E71" s="4">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I71" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="J71" s="4" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="3">
+      <c r="A72" s="4">
         <v>1070</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="4">
         <v>71</v>
       </c>
-      <c r="D72" s="3">
-        <v>1</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I72" s="3" t="s">
+      <c r="D72" s="4">
+        <v>1</v>
+      </c>
+      <c r="E72" s="4">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I72" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="J72" s="3" t="s">
+      <c r="J72" s="4" t="s">
         <v>691</v>
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="3">
+      <c r="A73" s="4">
         <v>1071</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73" s="4">
         <v>72</v>
       </c>
-      <c r="D73" s="3">
-        <v>1</v>
-      </c>
-      <c r="E73" s="3">
-        <v>0</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I73" s="3" t="s">
+      <c r="D73" s="4">
+        <v>1</v>
+      </c>
+      <c r="E73" s="4">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I73" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="J73" s="3" t="s">
+      <c r="J73" s="4" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="3">
+      <c r="A74" s="4">
         <v>1072</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="4">
         <v>73</v>
       </c>
-      <c r="D74" s="3">
-        <v>1</v>
-      </c>
-      <c r="E74" s="3">
-        <v>0</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I74" s="3" t="s">
+      <c r="D74" s="4">
+        <v>1</v>
+      </c>
+      <c r="E74" s="4">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I74" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="J74" s="3" t="s">
+      <c r="J74" s="4" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="3">
+      <c r="A75" s="4">
         <v>1073</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75" s="4">
         <v>74</v>
       </c>
-      <c r="D75" s="3">
-        <v>1</v>
-      </c>
-      <c r="E75" s="3">
-        <v>0</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I75" s="3" t="s">
+      <c r="D75" s="4">
+        <v>1</v>
+      </c>
+      <c r="E75" s="4">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I75" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="J75" s="3" t="s">
+      <c r="J75" s="4" t="s">
         <v>700</v>
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="3">
+      <c r="A76" s="4">
         <v>1074</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76" s="4">
         <v>75</v>
       </c>
-      <c r="D76" s="3">
-        <v>1</v>
-      </c>
-      <c r="E76" s="3">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I76" s="3" t="s">
+      <c r="D76" s="4">
+        <v>1</v>
+      </c>
+      <c r="E76" s="4">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I76" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="J76" s="4" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="3">
+      <c r="A77" s="4">
         <v>1075</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="C77" s="3">
+      <c r="C77" s="4">
         <v>76</v>
       </c>
-      <c r="D77" s="3">
-        <v>1</v>
-      </c>
-      <c r="E77" s="3">
-        <v>0</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I77" s="3" t="s">
+      <c r="D77" s="4">
+        <v>1</v>
+      </c>
+      <c r="E77" s="4">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I77" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="J77" s="4" t="s">
         <v>706</v>
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="3">
+      <c r="A78" s="4">
         <v>1076</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C78" s="4">
         <v>77</v>
       </c>
-      <c r="D78" s="3">
-        <v>1</v>
-      </c>
-      <c r="E78" s="3">
-        <v>0</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I78" s="3" t="s">
+      <c r="D78" s="4">
+        <v>1</v>
+      </c>
+      <c r="E78" s="4">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I78" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="J78" s="3" t="s">
+      <c r="J78" s="4" t="s">
         <v>709</v>
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="3">
+      <c r="A79" s="4">
         <v>1077</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="C79" s="3">
+      <c r="C79" s="4">
         <v>78</v>
       </c>
-      <c r="D79" s="3">
-        <v>1</v>
-      </c>
-      <c r="E79" s="3">
-        <v>0</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I79" s="3" t="s">
+      <c r="D79" s="4">
+        <v>1</v>
+      </c>
+      <c r="E79" s="4">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I79" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="J79" s="3" t="s">
+      <c r="J79" s="4" t="s">
         <v>712</v>
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="3">
+      <c r="A80" s="4">
         <v>1078</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="C80" s="3">
+      <c r="C80" s="4">
         <v>79</v>
       </c>
-      <c r="D80" s="3">
-        <v>1</v>
-      </c>
-      <c r="E80" s="3">
-        <v>0</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I80" s="3" t="s">
+      <c r="D80" s="4">
+        <v>1</v>
+      </c>
+      <c r="E80" s="4">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I80" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="J80" s="3" t="s">
+      <c r="J80" s="4" t="s">
         <v>715</v>
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="3">
+      <c r="A81" s="4">
         <v>1079</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="C81" s="3">
+      <c r="C81" s="4">
         <v>80</v>
       </c>
-      <c r="D81" s="3">
-        <v>1</v>
-      </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I81" s="3" t="s">
+      <c r="D81" s="4">
+        <v>1</v>
+      </c>
+      <c r="E81" s="4">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I81" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="J81" s="4" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="3">
+      <c r="A82" s="4">
         <v>1080</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="C82" s="3">
+      <c r="C82" s="4">
         <v>81</v>
       </c>
-      <c r="D82" s="3">
-        <v>1</v>
-      </c>
-      <c r="E82" s="3">
-        <v>0</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I82" s="3" t="s">
+      <c r="D82" s="4">
+        <v>1</v>
+      </c>
+      <c r="E82" s="4">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I82" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J82" s="3" t="s">
+      <c r="J82" s="4" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="3">
+      <c r="A83" s="4">
         <v>1081</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="C83" s="3">
+      <c r="C83" s="4">
         <v>82</v>
       </c>
-      <c r="D83" s="3">
-        <v>1</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I83" s="3" t="s">
+      <c r="D83" s="4">
+        <v>1</v>
+      </c>
+      <c r="E83" s="4">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I83" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="J83" s="4" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="3">
+      <c r="A84" s="4">
         <v>1082</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="C84" s="3">
+      <c r="C84" s="4">
         <v>83</v>
       </c>
-      <c r="D84" s="3">
-        <v>1</v>
-      </c>
-      <c r="E84" s="3">
-        <v>0</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I84" s="3" t="s">
+      <c r="D84" s="4">
+        <v>1</v>
+      </c>
+      <c r="E84" s="4">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I84" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="J84" s="3" t="s">
+      <c r="J84" s="4" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="3">
+      <c r="A85" s="4">
         <v>1083</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="C85" s="3">
+      <c r="C85" s="4">
         <v>84</v>
       </c>
-      <c r="D85" s="3">
-        <v>1</v>
-      </c>
-      <c r="E85" s="3">
-        <v>0</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I85" s="3" t="s">
+      <c r="D85" s="4">
+        <v>1</v>
+      </c>
+      <c r="E85" s="4">
+        <v>0</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="J85" s="3" t="s">
+      <c r="J85" s="4" t="s">
         <v>723</v>
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="3">
+      <c r="A86" s="4">
         <v>1084</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="C86" s="3">
+      <c r="C86" s="4">
         <v>85</v>
       </c>
-      <c r="D86" s="3">
-        <v>1</v>
-      </c>
-      <c r="E86" s="3">
-        <v>0</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I86" s="3" t="s">
+      <c r="D86" s="4">
+        <v>1</v>
+      </c>
+      <c r="E86" s="4">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I86" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="J86" s="3" t="s">
+      <c r="J86" s="4" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="3">
+      <c r="A87" s="4">
         <v>1085</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="C87" s="3">
+      <c r="C87" s="4">
         <v>86</v>
       </c>
-      <c r="D87" s="3">
-        <v>1</v>
-      </c>
-      <c r="E87" s="3">
-        <v>0</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I87" s="3" t="s">
+      <c r="D87" s="4">
+        <v>1</v>
+      </c>
+      <c r="E87" s="4">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I87" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="J87" s="3" t="s">
+      <c r="J87" s="4" t="s">
         <v>729</v>
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="3">
+      <c r="A88" s="4">
         <v>1086</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="C88" s="3">
+      <c r="C88" s="4">
         <v>87</v>
       </c>
-      <c r="D88" s="3">
-        <v>1</v>
-      </c>
-      <c r="E88" s="3">
-        <v>0</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I88" s="3" t="s">
+      <c r="D88" s="4">
+        <v>1</v>
+      </c>
+      <c r="E88" s="4">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I88" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="J88" s="3" t="s">
+      <c r="J88" s="4" t="s">
         <v>732</v>
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="3">
+      <c r="A89" s="4">
         <v>1087</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="C89" s="3">
+      <c r="C89" s="4">
         <v>88</v>
       </c>
-      <c r="D89" s="3">
-        <v>1</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I89" s="3" t="s">
+      <c r="D89" s="4">
+        <v>1</v>
+      </c>
+      <c r="E89" s="4">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I89" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="J89" s="3" t="s">
+      <c r="J89" s="4" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="3">
+      <c r="A90" s="4">
         <v>1088</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="C90" s="3">
+      <c r="C90" s="4">
         <v>89</v>
       </c>
-      <c r="D90" s="3">
-        <v>1</v>
-      </c>
-      <c r="E90" s="3">
-        <v>0</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I90" s="3" t="s">
+      <c r="D90" s="4">
+        <v>1</v>
+      </c>
+      <c r="E90" s="4">
+        <v>0</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I90" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="J90" s="3" t="s">
+      <c r="J90" s="4" t="s">
         <v>738</v>
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="3">
+      <c r="A91" s="4">
         <v>1089</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="4" t="s">
         <v>739</v>
       </c>
-      <c r="C91" s="3">
+      <c r="C91" s="4">
         <v>90</v>
       </c>
-      <c r="D91" s="3">
-        <v>1</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I91" s="3" t="s">
+      <c r="D91" s="4">
+        <v>1</v>
+      </c>
+      <c r="E91" s="4">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I91" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="J91" s="4" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="3">
+      <c r="A92" s="4">
         <v>1090</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="C92" s="3">
+      <c r="C92" s="4">
         <v>91</v>
       </c>
-      <c r="D92" s="3">
-        <v>1</v>
-      </c>
-      <c r="E92" s="3">
-        <v>0</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I92" s="3" t="s">
+      <c r="D92" s="4">
+        <v>1</v>
+      </c>
+      <c r="E92" s="4">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I92" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="J92" s="3" t="s">
+      <c r="J92" s="4" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="3">
+      <c r="A93" s="4">
         <v>1091</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="C93" s="3">
+      <c r="C93" s="4">
         <v>92</v>
       </c>
-      <c r="D93" s="3">
-        <v>1</v>
-      </c>
-      <c r="E93" s="3">
-        <v>0</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I93" s="3" t="s">
+      <c r="D93" s="4">
+        <v>1</v>
+      </c>
+      <c r="E93" s="4">
+        <v>0</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I93" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="J93" s="3" t="s">
+      <c r="J93" s="4" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="3">
+      <c r="A94" s="4">
         <v>1092</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="C94" s="3">
+      <c r="C94" s="4">
         <v>93</v>
       </c>
-      <c r="D94" s="3">
-        <v>1</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I94" s="3" t="s">
+      <c r="D94" s="4">
+        <v>1</v>
+      </c>
+      <c r="E94" s="4">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I94" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="J94" s="3" t="s">
+      <c r="J94" s="4" t="s">
         <v>750</v>
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="3">
+      <c r="A95" s="4">
         <v>1093</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="C95" s="3">
+      <c r="C95" s="4">
         <v>94</v>
       </c>
-      <c r="D95" s="3">
-        <v>1</v>
-      </c>
-      <c r="E95" s="3">
-        <v>0</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I95" s="3" t="s">
+      <c r="D95" s="4">
+        <v>1</v>
+      </c>
+      <c r="E95" s="4">
+        <v>0</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I95" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="J95" s="3" t="s">
+      <c r="J95" s="4" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="3">
+      <c r="A96" s="4">
         <v>1094</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="C96" s="3">
+      <c r="C96" s="4">
         <v>95</v>
       </c>
-      <c r="D96" s="3">
-        <v>1</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I96" s="3" t="s">
+      <c r="D96" s="4">
+        <v>1</v>
+      </c>
+      <c r="E96" s="4">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I96" s="4" t="s">
         <v>755</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="J96" s="4" t="s">
         <v>756</v>
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="3">
+      <c r="A97" s="4">
         <v>1095</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="4" t="s">
         <v>757</v>
       </c>
-      <c r="C97" s="3">
+      <c r="C97" s="4">
         <v>96</v>
       </c>
-      <c r="D97" s="3">
-        <v>1</v>
-      </c>
-      <c r="E97" s="3">
-        <v>0</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I97" s="3" t="s">
+      <c r="D97" s="4">
+        <v>1</v>
+      </c>
+      <c r="E97" s="4">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I97" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="J97" s="3" t="s">
+      <c r="J97" s="4" t="s">
         <v>758</v>
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="3">
+      <c r="A98" s="4">
         <v>1096</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="4" t="s">
         <v>757</v>
       </c>
-      <c r="C98" s="3">
+      <c r="C98" s="4">
         <v>97</v>
       </c>
-      <c r="D98" s="3">
-        <v>1</v>
-      </c>
-      <c r="E98" s="3">
-        <v>0</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I98" s="3" t="s">
+      <c r="D98" s="4">
+        <v>1</v>
+      </c>
+      <c r="E98" s="4">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I98" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="J98" s="3" t="s">
+      <c r="J98" s="4" t="s">
         <v>758</v>
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="3">
+      <c r="A99" s="4">
         <v>1097</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="4" t="s">
         <v>757</v>
       </c>
-      <c r="C99" s="3">
+      <c r="C99" s="4">
         <v>98</v>
       </c>
-      <c r="D99" s="3">
-        <v>1</v>
-      </c>
-      <c r="E99" s="3">
-        <v>0</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I99" s="3" t="s">
+      <c r="D99" s="4">
+        <v>1</v>
+      </c>
+      <c r="E99" s="4">
+        <v>0</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I99" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="J99" s="3" t="s">
+      <c r="J99" s="4" t="s">
         <v>758</v>
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="3">
+      <c r="A100" s="4">
         <v>1098</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="4" t="s">
         <v>759</v>
       </c>
-      <c r="C100" s="3">
+      <c r="C100" s="4">
         <v>99</v>
       </c>
-      <c r="D100" s="3">
-        <v>1</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I100" s="3" t="s">
+      <c r="D100" s="4">
+        <v>1</v>
+      </c>
+      <c r="E100" s="4">
+        <v>0</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I100" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="J100" s="3" t="s">
+      <c r="J100" s="4" t="s">
         <v>761</v>
       </c>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="3">
+      <c r="A101" s="4">
         <v>1099</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="C101" s="3">
+      <c r="C101" s="4">
         <v>100</v>
       </c>
-      <c r="D101" s="3">
-        <v>1</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I101" s="3" t="s">
+      <c r="D101" s="4">
+        <v>1</v>
+      </c>
+      <c r="E101" s="4">
+        <v>0</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I101" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="J101" s="4" t="s">
         <v>764</v>
       </c>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="3">
+      <c r="A102" s="4">
         <v>1100</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="4" t="s">
         <v>765</v>
       </c>
-      <c r="C102" s="3">
+      <c r="C102" s="4">
         <v>101</v>
       </c>
-      <c r="D102" s="3">
-        <v>1</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I102" s="3" t="s">
+      <c r="D102" s="4">
+        <v>1</v>
+      </c>
+      <c r="E102" s="4">
+        <v>0</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I102" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="J102" s="3" t="s">
+      <c r="J102" s="4" t="s">
         <v>767</v>
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="3">
+      <c r="A103" s="4">
         <v>1101</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="C103" s="3">
+      <c r="C103" s="4">
         <v>102</v>
       </c>
-      <c r="D103" s="3">
-        <v>1</v>
-      </c>
-      <c r="E103" s="3">
-        <v>0</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I103" s="3" t="s">
+      <c r="D103" s="4">
+        <v>1</v>
+      </c>
+      <c r="E103" s="4">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I103" s="4" t="s">
         <v>769</v>
       </c>
-      <c r="J103" s="3" t="s">
+      <c r="J103" s="4" t="s">
         <v>770</v>
       </c>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="3">
+      <c r="A104" s="4">
         <v>1102</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="C104" s="3">
+      <c r="C104" s="4">
         <v>103</v>
       </c>
-      <c r="D104" s="3">
-        <v>1</v>
-      </c>
-      <c r="E104" s="3">
-        <v>0</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I104" s="3" t="s">
+      <c r="D104" s="4">
+        <v>1</v>
+      </c>
+      <c r="E104" s="4">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I104" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="J104" s="3" t="s">
+      <c r="J104" s="4" t="s">
         <v>773</v>
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="3">
+      <c r="A105" s="4">
         <v>1103</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="4" t="s">
         <v>774</v>
       </c>
-      <c r="C105" s="3">
+      <c r="C105" s="4">
         <v>104</v>
       </c>
-      <c r="D105" s="3">
-        <v>1</v>
-      </c>
-      <c r="E105" s="3">
-        <v>0</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I105" s="3" t="s">
+      <c r="D105" s="4">
+        <v>1</v>
+      </c>
+      <c r="E105" s="4">
+        <v>0</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I105" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="J105" s="3" t="s">
+      <c r="J105" s="4" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="3">
+      <c r="A106" s="4">
         <v>1104</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="C106" s="3">
+      <c r="C106" s="4">
         <v>105</v>
       </c>
-      <c r="D106" s="3">
-        <v>1</v>
-      </c>
-      <c r="E106" s="3">
-        <v>0</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I106" s="3" t="s">
+      <c r="D106" s="4">
+        <v>1</v>
+      </c>
+      <c r="E106" s="4">
+        <v>0</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I106" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="J106" s="3" t="s">
+      <c r="J106" s="4" t="s">
         <v>779</v>
       </c>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="3">
+      <c r="A107" s="4">
         <v>1105</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="C107" s="3">
+      <c r="C107" s="4">
         <v>106</v>
       </c>
-      <c r="D107" s="3">
-        <v>1</v>
-      </c>
-      <c r="E107" s="3">
-        <v>0</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I107" s="3" t="s">
+      <c r="D107" s="4">
+        <v>1</v>
+      </c>
+      <c r="E107" s="4">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I107" s="4" t="s">
         <v>781</v>
       </c>
-      <c r="J107" s="3" t="s">
+      <c r="J107" s="4" t="s">
         <v>782</v>
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="3">
+      <c r="A108" s="4">
         <v>1106</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="C108" s="3">
+      <c r="C108" s="4">
         <v>107</v>
       </c>
-      <c r="D108" s="3">
-        <v>1</v>
-      </c>
-      <c r="E108" s="3">
-        <v>0</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I108" s="3" t="s">
+      <c r="D108" s="4">
+        <v>1</v>
+      </c>
+      <c r="E108" s="4">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I108" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="J108" s="3" t="s">
+      <c r="J108" s="4" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="3">
+      <c r="A109" s="4">
         <v>1107</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="C109" s="3">
+      <c r="C109" s="4">
         <v>108</v>
       </c>
-      <c r="D109" s="3">
-        <v>1</v>
-      </c>
-      <c r="E109" s="3">
-        <v>0</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I109" s="3" t="s">
+      <c r="D109" s="4">
+        <v>1</v>
+      </c>
+      <c r="E109" s="4">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I109" s="4" t="s">
         <v>787</v>
       </c>
-      <c r="J109" s="3" t="s">
+      <c r="J109" s="4" t="s">
         <v>788</v>
       </c>
     </row>
@@ -12378,7 +12387,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -12389,7 +12398,7 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12420,16 +12429,19 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2">
         <v>3000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>24577</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -12447,21 +12459,24 @@
         <v>11</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>792</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>3001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C3" s="2">
-        <v>2</v>
+        <v>24578</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -12479,21 +12494,24 @@
         <v>11</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>3002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C4" s="2">
-        <v>3</v>
+        <v>24579</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -12511,10 +12529,13 @@
         <v>11</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>793</v>
       </c>
     </row>
   </sheetData>
